--- a/data/trans_orig/P14B23-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P14B23-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya depresión o ansiedad le limita en 2012</t>
+          <t>Población cuya depresión o ansiedad le limita en 2012 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8256</t>
+          <t>8310</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23381</t>
+          <t>23156</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48579</t>
+          <t>49482</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>78180</t>
+          <t>79923</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62886</t>
+          <t>61275</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>98378</t>
+          <t>95350</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>680088</t>
+          <t>680313</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>695213</t>
+          <t>695159</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>616705</t>
+          <t>614962</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>646306</t>
+          <t>645403</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1299976</t>
+          <t>1303004</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1335468</t>
+          <t>1337079</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19264</t>
+          <t>18185</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41229</t>
+          <t>42192</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68596</t>
+          <t>67428</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>106365</t>
+          <t>105326</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>94770</t>
+          <t>92969</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>137847</t>
+          <t>136389</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>975620</t>
+          <t>974657</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>997585</t>
+          <t>998664</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>920742</t>
+          <t>921781</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>958511</t>
+          <t>959679</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1906109</t>
+          <t>1907567</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1949186</t>
+          <t>1950987</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>8337</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29608</t>
+          <t>27906</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42169</t>
+          <t>42401</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71842</t>
+          <t>72264</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55663</t>
+          <t>57891</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89994</t>
+          <t>91943</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>728015</t>
+          <t>729717</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>749042</t>
+          <t>749286</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>704241</t>
+          <t>703819</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>733914</t>
+          <t>733682</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1443712</t>
+          <t>1441763</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1478043</t>
+          <t>1475815</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,23%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16321</t>
+          <t>17270</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37935</t>
+          <t>39142</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65038</t>
+          <t>65657</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101835</t>
+          <t>101308</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>88644</t>
+          <t>88828</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>128977</t>
+          <t>130126</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>908754</t>
+          <t>907547</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>930368</t>
+          <t>929419</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>947052</t>
+          <t>947579</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>983849</t>
+          <t>983230</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1866599</t>
+          <t>1865450</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1906932</t>
+          <t>1906748</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,55%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68163</t>
+          <t>67656</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>107992</t>
+          <t>107473</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>253008</t>
+          <t>251793</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>319642</t>
+          <t>317833</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>333642</t>
+          <t>336930</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>406157</t>
+          <t>414637</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3316638</t>
+          <t>3317157</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3356467</t>
+          <t>3356974</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3227321</t>
+          <t>3229130</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3293955</t>
+          <t>3295170</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6565435</t>
+          <t>6556955</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6637950</t>
+          <t>6634662</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya depresión o ansiedad le limita en 2016</t>
+          <t>Población cuya depresión o ansiedad le limita en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6773</t>
+          <t>6722</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21304</t>
+          <t>21740</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40786</t>
+          <t>40864</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>70235</t>
+          <t>70773</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52179</t>
+          <t>50944</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84336</t>
+          <t>81757</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>653496</t>
+          <t>653060</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>668027</t>
+          <t>668078</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>602604</t>
+          <t>602066</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>632053</t>
+          <t>631975</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1263303</t>
+          <t>1265882</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1295460</t>
+          <t>1296695</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>9624</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25473</t>
+          <t>26151</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49463</t>
+          <t>47306</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82025</t>
+          <t>80991</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62751</t>
+          <t>64932</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>99552</t>
+          <t>100113</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>996958</t>
+          <t>996280</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1012492</t>
+          <t>1012807</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>960888</t>
+          <t>961922</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>993450</t>
+          <t>995607</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1965792</t>
+          <t>1965231</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2002593</t>
+          <t>2000412</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,86%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11107</t>
+          <t>11067</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28272</t>
+          <t>28919</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40103</t>
+          <t>40674</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71745</t>
+          <t>70819</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56930</t>
+          <t>56315</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>90370</t>
+          <t>89893</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>731280</t>
+          <t>730633</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>748445</t>
+          <t>748485</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>713266</t>
+          <t>714192</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>744908</t>
+          <t>744337</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1454193</t>
+          <t>1454670</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1487633</t>
+          <t>1488248</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12397</t>
+          <t>12923</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31022</t>
+          <t>30822</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51486</t>
+          <t>50043</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83445</t>
+          <t>84111</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>68750</t>
+          <t>68464</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107358</t>
+          <t>105742</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>906545</t>
+          <t>906745</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>925170</t>
+          <t>924644</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>960334</t>
+          <t>959668</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>992293</t>
+          <t>993736</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1873988</t>
+          <t>1875604</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1912596</t>
+          <t>1912882</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>53009</t>
+          <t>51745</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85211</t>
+          <t>84366</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>208193</t>
+          <t>206790</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>268155</t>
+          <t>268244</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>270864</t>
+          <t>273416</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>340407</t>
+          <t>340593</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3309139</t>
+          <t>3309984</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3341341</t>
+          <t>3342605</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3276387</t>
+          <t>3276298</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3336349</t>
+          <t>3337752</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6598485</t>
+          <t>6598299</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6668028</t>
+          <t>6665476</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya depresión o ansiedad le limita en 2023</t>
+          <t>Población cuya depresión o ansiedad le limita en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25570</t>
+          <t>25671</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49158</t>
+          <t>50130</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34852</t>
+          <t>35239</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57305</t>
+          <t>57467</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>66291</t>
+          <t>67374</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>98524</t>
+          <t>99841</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>586283</t>
+          <t>585311</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>609871</t>
+          <t>609770</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>668025</t>
+          <t>667863</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>690478</t>
+          <t>690091</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1262248</t>
+          <t>1260931</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1294481</t>
+          <t>1293398</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11747</t>
+          <t>12284</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>39686</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56965</t>
+          <t>57171</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83042</t>
+          <t>83692</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64612</t>
+          <t>64016</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>114218</t>
+          <t>115546</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1153852</t>
+          <t>1153178</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1181117</t>
+          <t>1180580</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>875609</t>
+          <t>874959</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>901686</t>
+          <t>901480</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2037298</t>
+          <t>2035970</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2086904</t>
+          <t>2087500</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15379</t>
+          <t>14997</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36994</t>
+          <t>38443</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35014</t>
+          <t>31361</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>92976</t>
+          <t>93173</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60346</t>
+          <t>60923</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>113654</t>
+          <t>115249</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>667686</t>
+          <t>666237</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>689301</t>
+          <t>689683</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>840390</t>
+          <t>840193</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>898352</t>
+          <t>902005</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1524392</t>
+          <t>1522797</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1577700</t>
+          <t>1577123</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,28%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28242</t>
+          <t>30176</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53117</t>
+          <t>53410</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66936</t>
+          <t>66696</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101781</t>
+          <t>104138</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>106560</t>
+          <t>105713</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>148517</t>
+          <t>147662</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>873714</t>
+          <t>873421</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>898589</t>
+          <t>896655</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>993151</t>
+          <t>990794</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1027996</t>
+          <t>1028236</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1873246</t>
+          <t>1874101</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1915203</t>
+          <t>1916050</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97311</t>
+          <t>95568</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>153069</t>
+          <t>151131</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>214393</t>
+          <t>217540</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>300328</t>
+          <t>301198</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>344408</t>
+          <t>345309</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>437020</t>
+          <t>440752</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3306748</t>
+          <t>3308686</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3362506</t>
+          <t>3364249</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3411952</t>
+          <t>3411082</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3497887</t>
+          <t>3494740</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6735077</t>
+          <t>6731345</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6827689</t>
+          <t>6826788</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P14B23-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P14B23-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>7924</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23156</t>
+          <t>23106</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>49482</t>
+          <t>48589</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79923</t>
+          <t>79151</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61275</t>
+          <t>62752</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95350</t>
+          <t>95641</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>680313</t>
+          <t>680363</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>695159</t>
+          <t>695545</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>614962</t>
+          <t>615734</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>645403</t>
+          <t>646296</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1303004</t>
+          <t>1302713</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1337079</t>
+          <t>1335602</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18185</t>
+          <t>19071</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42192</t>
+          <t>40811</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67428</t>
+          <t>66747</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105326</t>
+          <t>102708</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>92969</t>
+          <t>92331</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>136389</t>
+          <t>135689</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>974657</t>
+          <t>976038</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>998664</t>
+          <t>997778</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>921781</t>
+          <t>924399</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>959679</t>
+          <t>960360</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1907567</t>
+          <t>1908267</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1950987</t>
+          <t>1951625</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8337</t>
+          <t>8597</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27906</t>
+          <t>29286</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42401</t>
+          <t>43415</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72264</t>
+          <t>73330</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57891</t>
+          <t>56245</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91943</t>
+          <t>91347</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>729717</t>
+          <t>728337</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>749286</t>
+          <t>749026</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>703819</t>
+          <t>702753</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>733682</t>
+          <t>732668</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1441763</t>
+          <t>1442359</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1475815</t>
+          <t>1477461</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17270</t>
+          <t>17067</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39142</t>
+          <t>38006</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65657</t>
+          <t>66297</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101308</t>
+          <t>102023</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>88828</t>
+          <t>86747</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130126</t>
+          <t>131670</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>907547</t>
+          <t>908683</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>929419</t>
+          <t>929622</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>947579</t>
+          <t>946864</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>983230</t>
+          <t>982590</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1865450</t>
+          <t>1863906</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1906748</t>
+          <t>1908829</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,65%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>67656</t>
+          <t>69133</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>107473</t>
+          <t>108333</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>251793</t>
+          <t>255069</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>317833</t>
+          <t>317908</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>336930</t>
+          <t>334280</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>414637</t>
+          <t>407596</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3317157</t>
+          <t>3316297</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3356974</t>
+          <t>3355497</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3229130</t>
+          <t>3229055</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3295170</t>
+          <t>3291894</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6556955</t>
+          <t>6563996</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6634662</t>
+          <t>6637312</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,21%</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21740</t>
+          <t>20596</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40864</t>
+          <t>39901</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>70773</t>
+          <t>69619</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50944</t>
+          <t>51751</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81757</t>
+          <t>84275</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>653060</t>
+          <t>654204</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>602066</t>
+          <t>603220</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>631975</t>
+          <t>632938</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1265882</t>
+          <t>1263364</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1296695</t>
+          <t>1295888</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9624</t>
+          <t>10099</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26151</t>
+          <t>25747</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47306</t>
+          <t>48726</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80991</t>
+          <t>81669</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64932</t>
+          <t>62722</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>100113</t>
+          <t>100730</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>996280</t>
+          <t>996684</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1012807</t>
+          <t>1012332</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>961922</t>
+          <t>961244</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>995607</t>
+          <t>994187</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1965231</t>
+          <t>1964614</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2000412</t>
+          <t>2002622</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11067</t>
+          <t>11033</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28919</t>
+          <t>29686</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40674</t>
+          <t>39374</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70819</t>
+          <t>68618</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56315</t>
+          <t>55651</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89893</t>
+          <t>88594</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>730633</t>
+          <t>729866</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>748485</t>
+          <t>748519</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>714192</t>
+          <t>716393</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>744337</t>
+          <t>745637</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1454670</t>
+          <t>1455969</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1488248</t>
+          <t>1488912</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12923</t>
+          <t>12765</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30822</t>
+          <t>29735</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50043</t>
+          <t>51074</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84111</t>
+          <t>85720</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>68464</t>
+          <t>70048</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>105742</t>
+          <t>107717</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>906745</t>
+          <t>907832</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>924644</t>
+          <t>924802</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>959668</t>
+          <t>958059</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>993736</t>
+          <t>992705</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1875604</t>
+          <t>1873629</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1912882</t>
+          <t>1911298</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51745</t>
+          <t>51778</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>84366</t>
+          <t>86034</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>206790</t>
+          <t>207921</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>268244</t>
+          <t>270549</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>273416</t>
+          <t>271816</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>340593</t>
+          <t>345097</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3309984</t>
+          <t>3308316</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3342605</t>
+          <t>3342572</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3276298</t>
+          <t>3273993</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3337752</t>
+          <t>3336621</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6598299</t>
+          <t>6593795</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6665476</t>
+          <t>6667076</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,08%</t>
         </is>
       </c>
     </row>
@@ -4621,32 +4621,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>35765</t>
+          <t>38611</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25671</t>
+          <t>27803</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50130</t>
+          <t>52533</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4656,32 +4656,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>45787</t>
+          <t>49974</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35239</t>
+          <t>40408</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57467</t>
+          <t>60777</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4691,32 +4691,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>81553</t>
+          <t>88586</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>67374</t>
+          <t>73972</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>99841</t>
+          <t>109079</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -4734,32 +4734,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>599676</t>
+          <t>652099</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>585311</t>
+          <t>638177</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>609770</t>
+          <t>662907</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4769,32 +4769,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>679543</t>
+          <t>684206</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>667863</t>
+          <t>673403</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>690091</t>
+          <t>693772</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1279219</t>
+          <t>1336303</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1260931</t>
+          <t>1315810</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1293398</t>
+          <t>1350917</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,81%</t>
         </is>
       </c>
     </row>
@@ -4847,17 +4847,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4882,17 +4882,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4964,32 +4964,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25329</t>
+          <t>25924</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12284</t>
+          <t>17239</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39686</t>
+          <t>37537</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4999,32 +4999,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>69318</t>
+          <t>76288</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57171</t>
+          <t>63189</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83692</t>
+          <t>90251</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5034,32 +5034,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>94647</t>
+          <t>102212</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64016</t>
+          <t>86036</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>115546</t>
+          <t>120921</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -5077,32 +5077,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1167535</t>
+          <t>1022993</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1153178</t>
+          <t>1011380</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1180580</t>
+          <t>1031678</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5112,32 +5112,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>889333</t>
+          <t>995186</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>874959</t>
+          <t>981223</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>901480</t>
+          <t>1008285</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2056869</t>
+          <t>2018179</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2035970</t>
+          <t>1999470</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2087500</t>
+          <t>2034355</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>95,94%</t>
         </is>
       </c>
     </row>
@@ -5190,17 +5190,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5225,17 +5225,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5260,17 +5260,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5307,32 +5307,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>24135</t>
+          <t>27129</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14997</t>
+          <t>17853</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38443</t>
+          <t>42876</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5342,32 +5342,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>67776</t>
+          <t>78086</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31361</t>
+          <t>64160</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>93173</t>
+          <t>93570</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5377,32 +5377,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>91911</t>
+          <t>105215</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60923</t>
+          <t>86804</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>115249</t>
+          <t>126914</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -5420,32 +5420,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>680545</t>
+          <t>775944</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>666237</t>
+          <t>760197</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>689683</t>
+          <t>785220</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5455,32 +5455,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>865590</t>
+          <t>734173</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>840193</t>
+          <t>718689</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>902005</t>
+          <t>748099</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1546135</t>
+          <t>1510117</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1522797</t>
+          <t>1488418</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1577123</t>
+          <t>1528528</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>94,63%</t>
         </is>
       </c>
     </row>
@@ -5533,17 +5533,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>40573</t>
+          <t>43553</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30176</t>
+          <t>33289</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53410</t>
+          <t>58692</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>85550</t>
+          <t>94982</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66696</t>
+          <t>79962</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>104138</t>
+          <t>112912</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>126123</t>
+          <t>138535</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>105713</t>
+          <t>118268</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>147662</t>
+          <t>159280</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -5763,32 +5763,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>886258</t>
+          <t>946509</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>873421</t>
+          <t>931370</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>896655</t>
+          <t>956773</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5798,32 +5798,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1009382</t>
+          <t>1024059</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>990794</t>
+          <t>1006129</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1028236</t>
+          <t>1039079</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1895640</t>
+          <t>1970569</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1874101</t>
+          <t>1949824</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1916050</t>
+          <t>1990836</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -5876,17 +5876,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5911,17 +5911,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>125802</t>
+          <t>135218</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>95568</t>
+          <t>110878</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>151131</t>
+          <t>160747</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>268431</t>
+          <t>299330</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>217540</t>
+          <t>272183</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>301198</t>
+          <t>328950</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>394233</t>
+          <t>434548</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>345309</t>
+          <t>394765</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>440752</t>
+          <t>470025</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -6106,32 +6106,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3334015</t>
+          <t>3397544</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3308686</t>
+          <t>3372015</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3364249</t>
+          <t>3421884</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6141,32 +6141,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3443849</t>
+          <t>3437624</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3411082</t>
+          <t>3408004</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3494740</t>
+          <t>3464771</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6777864</t>
+          <t>6835168</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6731345</t>
+          <t>6799691</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6826788</t>
+          <t>6874951</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>94,57%</t>
         </is>
       </c>
     </row>
@@ -6219,17 +6219,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6254,17 +6254,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
